--- a/download/input.xlsx
+++ b/download/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED6FBFB-F392-4F42-9AF9-A396944F21FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBE94AF-2BDD-433E-9A3C-FCC319DC2256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Instructions" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$207</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="380">
   <si>
     <t>id</t>
   </si>
@@ -271,9 +271,6 @@
     <t>4QF 1 с.ш. ГРЩ1</t>
   </si>
   <si>
-    <t>QF18 2 с.ш. ППУ</t>
-  </si>
-  <si>
     <t>QF1 ввод ППУ-п</t>
   </si>
   <si>
@@ -946,9 +943,6 @@
     <t>Узуч 1 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
   </si>
   <si>
-    <t>Узуч 2 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
-  </si>
-  <si>
     <t>Узел QF3 2 с.ш. ГРЩ1/ Узел QF3 1 с.ш. ППУ/QF6 2 с.ш. ППУ ГРЩ1</t>
   </si>
   <si>
@@ -1087,9 +1081,6 @@
     <t>QF13 2 с.ш. ШАУ-П ППУ</t>
   </si>
   <si>
-    <t>QF1 1 с.ш.-ТЦ</t>
-  </si>
-  <si>
     <t>QF1 1 с.ш.-ТЦ ППУ</t>
   </si>
   <si>
@@ -1150,9 +1141,6 @@
     <t>нагрузка 10</t>
   </si>
   <si>
-    <t>нагрузка 11</t>
-  </si>
-  <si>
     <t>нагрузка 12</t>
   </si>
   <si>
@@ -1181,6 +1169,9 @@
   </si>
   <si>
     <t>Кабель 5*4</t>
+  </si>
+  <si>
+    <t>Учет 2 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K985"/>
+  <dimension ref="A1:K983"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.875" customWidth="1"/>
@@ -1760,7 +1751,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>4</v>
@@ -1801,7 +1792,7 @@
         <v>59</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G2" s="5">
         <v>1000</v>
@@ -1834,7 +1825,7 @@
         <v>62</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G3" s="5">
         <v>630</v>
@@ -1861,10 +1852,10 @@
         <v>59</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>59</v>
@@ -1891,13 +1882,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>59</v>
@@ -1924,10 +1915,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>60</v>
@@ -1957,13 +1948,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="5">
@@ -1991,10 +1982,10 @@
         <v>60</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>59</v>
@@ -2010,22 +2001,22 @@
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="26.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="5"/>
@@ -2033,7 +2024,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
       <c r="K9" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="26.25">
@@ -2047,7 +2038,7 @@
         <v>61</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>73</v>
@@ -2060,7 +2051,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="26.25">
@@ -2074,7 +2065,7 @@
         <v>61</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>66</v>
@@ -2087,7 +2078,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="26.25">
@@ -2101,10 +2092,10 @@
         <v>62</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>62</v>
@@ -2125,13 +2116,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>62</v>
@@ -2141,7 +2132,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="26.25">
@@ -2152,10 +2143,10 @@
         <v>18</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>63</v>
@@ -2182,10 +2173,10 @@
         <v>63</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>62</v>
@@ -2194,10 +2185,10 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2206,13 +2197,13 @@
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>302</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="5"/>
@@ -2220,7 +2211,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
       <c r="K16" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2231,10 +2222,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>65</v>
@@ -2247,7 +2238,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="6"/>
       <c r="K17" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2258,10 +2249,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>67</v>
@@ -2274,7 +2265,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="6"/>
       <c r="K18" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30">
@@ -2288,7 +2279,7 @@
         <v>65</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>74</v>
@@ -2300,10 +2291,10 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30">
@@ -2317,7 +2308,7 @@
         <v>66</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>75</v>
@@ -2329,10 +2320,10 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2346,7 +2337,7 @@
         <v>67</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>75</v>
@@ -2358,7 +2349,7 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>17</v>
@@ -2372,20 +2363,20 @@
         <v>11</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>17</v>
@@ -2399,20 +2390,22 @@
         <v>11</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F23" s="16"/>
+        <v>379</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>17</v>
@@ -2429,20 +2422,20 @@
         <v>71</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="22"/>
       <c r="K24" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5">
@@ -2451,10 +2444,10 @@
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E25" s="21" t="s">
         <v>70</v>
@@ -2476,10 +2469,10 @@
         <v>11</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26" s="21" t="s">
         <v>76</v>
@@ -2499,13 +2492,13 @@
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="5"/>
@@ -2522,10 +2515,10 @@
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E28" s="21" t="s">
         <v>72</v>
@@ -2536,7 +2529,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="6"/>
       <c r="K28" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2550,7 +2543,7 @@
         <v>72</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E29" s="21" t="s">
         <v>74</v>
@@ -2561,7 +2554,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="6"/>
       <c r="K29" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2570,10 +2563,10 @@
       </c>
       <c r="B30" s="23"/>
       <c r="C30" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E30" s="21" t="s">
         <v>64</v>
@@ -2584,7 +2577,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="6"/>
       <c r="K30" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2598,7 +2591,7 @@
         <v>64</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>75</v>
@@ -2609,7 +2602,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="6"/>
       <c r="K31" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30">
@@ -2623,22 +2616,22 @@
         <v>72</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>74</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30">
@@ -2652,22 +2645,22 @@
         <v>65</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>74</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="30">
@@ -2681,22 +2674,22 @@
         <v>73</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>74</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="26.25">
@@ -2710,20 +2703,20 @@
         <v>74</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="6"/>
       <c r="K35" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="26.25">
@@ -2737,20 +2730,20 @@
         <v>74</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
       <c r="K36" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="26.25">
@@ -2764,20 +2757,20 @@
         <v>74</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="6"/>
       <c r="K37" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="26.25">
@@ -2791,20 +2784,20 @@
         <v>74</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="6"/>
       <c r="K38" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="26.25">
@@ -2818,20 +2811,20 @@
         <v>74</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="6"/>
       <c r="K39" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="26.25">
@@ -2845,20 +2838,20 @@
         <v>74</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="6"/>
       <c r="K40" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="26.25">
@@ -2872,20 +2865,20 @@
         <v>74</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="6"/>
       <c r="K41" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="26.25">
@@ -2899,20 +2892,20 @@
         <v>74</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="6"/>
       <c r="K42" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="26.25">
@@ -2926,20 +2919,20 @@
         <v>75</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="6"/>
       <c r="K43" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="26.25">
@@ -2953,20 +2946,20 @@
         <v>75</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="6"/>
       <c r="K44" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="26.25">
@@ -2980,20 +2973,20 @@
         <v>75</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="6"/>
       <c r="K45" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="51.75">
@@ -3007,20 +3000,20 @@
         <v>72</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="6"/>
       <c r="K46" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="26.25">
@@ -3034,20 +3027,20 @@
         <v>75</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="6"/>
       <c r="K47" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="26.25">
@@ -3061,20 +3054,20 @@
         <v>75</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="6"/>
       <c r="K48" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="26.25">
@@ -3088,20 +3081,20 @@
         <v>75</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="6"/>
       <c r="K49" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="26.25">
@@ -3115,20 +3108,20 @@
         <v>75</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="6"/>
       <c r="K50" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="26.25">
@@ -3142,20 +3135,20 @@
         <v>75</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="6"/>
       <c r="K51" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="26.25">
@@ -3169,20 +3162,20 @@
         <v>75</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="6"/>
       <c r="K52" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="26.25">
@@ -3196,20 +3189,20 @@
         <v>75</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="6"/>
       <c r="K53" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="26.25">
@@ -3223,20 +3216,20 @@
         <v>75</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="6"/>
       <c r="K54" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="26.25">
@@ -3250,20 +3243,20 @@
         <v>75</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="6"/>
       <c r="K55" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="26.25">
@@ -3277,20 +3270,20 @@
         <v>75</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="6"/>
       <c r="K56" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="26.25">
@@ -3304,13 +3297,13 @@
         <v>16</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G57" s="5">
         <v>120</v>
@@ -3333,13 +3326,13 @@
         <v>16</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G58" s="5">
         <v>120</v>
@@ -3362,13 +3355,13 @@
         <v>16</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G59" s="5">
         <v>120</v>
@@ -3391,13 +3384,13 @@
         <v>16</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G60" s="5">
         <v>120</v>
@@ -3420,13 +3413,13 @@
         <v>16</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G61" s="5">
         <v>120</v>
@@ -3449,13 +3442,13 @@
         <v>16</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G62" s="5">
         <v>120</v>
@@ -3478,13 +3471,13 @@
         <v>16</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G63" s="5">
         <v>120</v>
@@ -3507,13 +3500,13 @@
         <v>16</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G64" s="5">
         <v>120</v>
@@ -3536,13 +3529,13 @@
         <v>16</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G65" s="5">
         <v>120</v>
@@ -3565,13 +3558,13 @@
         <v>16</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G66" s="5">
         <v>120</v>
@@ -3594,13 +3587,13 @@
         <v>16</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G67" s="5">
         <v>120</v>
@@ -3623,13 +3616,13 @@
         <v>76</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G68" s="5">
         <v>120</v>
@@ -3652,13 +3645,13 @@
         <v>76</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G69" s="5">
         <v>120</v>
@@ -3681,13 +3674,13 @@
         <v>76</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G70" s="5">
         <v>120</v>
@@ -3710,13 +3703,13 @@
         <v>76</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G71" s="5">
         <v>120</v>
@@ -3739,13 +3732,13 @@
         <v>76</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G72" s="5">
         <v>120</v>
@@ -3768,13 +3761,13 @@
         <v>76</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G73" s="5">
         <v>120</v>
@@ -3797,13 +3790,13 @@
         <v>76</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G74" s="5">
         <v>120</v>
@@ -3826,13 +3819,13 @@
         <v>76</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G75" s="5">
         <v>120</v>
@@ -3855,13 +3848,13 @@
         <v>76</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G76" s="5">
         <v>120</v>
@@ -3884,13 +3877,13 @@
         <v>76</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G77" s="5">
         <v>120</v>
@@ -3913,13 +3906,13 @@
         <v>16</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G78" s="5">
         <v>200</v>
@@ -3942,13 +3935,13 @@
         <v>77</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>78</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -3969,7 +3962,7 @@
         <v>78</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>76</v>
@@ -3979,7 +3972,7 @@
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K80" s="5" t="s">
         <v>17</v>
@@ -3993,23 +3986,23 @@
         <v>57</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="6"/>
       <c r="K81" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4020,23 +4013,23 @@
         <v>11</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="6"/>
       <c r="K82" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4047,23 +4040,23 @@
         <v>57</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="6"/>
       <c r="K83" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -4074,23 +4067,23 @@
         <v>11</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="6"/>
       <c r="K84" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -4101,23 +4094,23 @@
         <v>57</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="6"/>
       <c r="K85" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4128,25 +4121,25 @@
         <v>11</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -4157,25 +4150,25 @@
         <v>57</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="26.25">
@@ -4186,23 +4179,23 @@
         <v>11</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="6"/>
       <c r="K88" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="26.25">
@@ -4213,23 +4206,23 @@
         <v>11</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="6"/>
       <c r="K89" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="26.25">
@@ -4240,23 +4233,23 @@
         <v>11</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="18"/>
       <c r="K90" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="26.25">
@@ -4267,23 +4260,23 @@
         <v>11</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="18"/>
       <c r="K91" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="26.25">
@@ -4294,23 +4287,23 @@
         <v>11</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="18"/>
       <c r="K92" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="26.25">
@@ -4321,23 +4314,23 @@
         <v>11</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="18"/>
       <c r="K93" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="26.25">
@@ -4348,23 +4341,23 @@
         <v>11</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="18"/>
       <c r="K94" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="26.25">
@@ -4375,23 +4368,23 @@
         <v>11</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="18"/>
       <c r="K95" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="26.25">
@@ -4402,23 +4395,23 @@
         <v>11</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="18"/>
       <c r="K96" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="26.25">
@@ -4429,23 +4422,23 @@
         <v>11</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="18"/>
       <c r="K97" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="26.25">
@@ -4456,23 +4449,23 @@
         <v>11</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="18"/>
       <c r="K98" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="26.25">
@@ -4483,23 +4476,23 @@
         <v>57</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="18"/>
       <c r="K99" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="26.25">
@@ -4510,23 +4503,23 @@
         <v>11</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="18"/>
       <c r="K100" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="26.25">
@@ -4537,23 +4530,23 @@
         <v>11</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="18"/>
       <c r="K101" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="26.25">
@@ -4564,23 +4557,23 @@
         <v>11</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="18"/>
       <c r="K102" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="26.25">
@@ -4591,23 +4584,23 @@
         <v>11</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="18"/>
       <c r="K103" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="26.25">
@@ -4618,23 +4611,23 @@
         <v>57</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="18"/>
       <c r="K104" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="26.25">
@@ -4645,23 +4638,23 @@
         <v>11</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="18"/>
       <c r="K105" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="26.25">
@@ -4672,23 +4665,23 @@
         <v>11</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="18"/>
       <c r="K106" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="26.25">
@@ -4699,23 +4692,23 @@
         <v>11</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="18"/>
       <c r="K107" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="26.25">
@@ -4726,23 +4719,23 @@
         <v>57</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="18"/>
       <c r="K108" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="26.25">
@@ -4753,23 +4746,23 @@
         <v>11</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="18"/>
       <c r="K109" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="26.25">
@@ -4780,23 +4773,23 @@
         <v>11</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="18"/>
       <c r="K110" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="26.25">
@@ -4807,23 +4800,23 @@
         <v>11</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="18"/>
       <c r="K111" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="26.25">
@@ -4834,23 +4827,23 @@
         <v>11</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="18"/>
       <c r="K112" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="26.25">
@@ -4861,23 +4854,23 @@
         <v>11</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="18"/>
       <c r="K113" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="26.25">
@@ -4888,23 +4881,23 @@
         <v>11</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="18"/>
       <c r="K114" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="26.25">
@@ -4915,23 +4908,23 @@
         <v>11</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="18"/>
       <c r="K115" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="26.25">
@@ -4942,23 +4935,23 @@
         <v>11</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="18"/>
       <c r="K116" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="26.25">
@@ -4969,23 +4962,23 @@
         <v>11</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="18"/>
       <c r="K117" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="26.25">
@@ -4996,23 +4989,23 @@
         <v>11</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="18"/>
       <c r="K118" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="26.25">
@@ -5023,23 +5016,23 @@
         <v>11</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="18"/>
       <c r="K119" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="39">
@@ -5050,23 +5043,23 @@
         <v>11</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="18"/>
       <c r="K120" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -5077,11 +5070,11 @@
         <v>57</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D121" s="25"/>
       <c r="E121" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F121" s="25"/>
       <c r="G121" s="5"/>
@@ -5089,7 +5082,7 @@
       <c r="I121" s="5"/>
       <c r="J121" s="18"/>
       <c r="K121" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="64.5">
@@ -5100,23 +5093,23 @@
         <v>11</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="18"/>
       <c r="K122" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="64.5">
@@ -5127,23 +5120,23 @@
         <v>11</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="18"/>
       <c r="K123" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="51.75">
@@ -5154,23 +5147,23 @@
         <v>11</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="18"/>
       <c r="K124" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="39">
@@ -5181,23 +5174,23 @@
         <v>11</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="18"/>
       <c r="K125" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5208,11 +5201,11 @@
         <v>57</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D126" s="25"/>
       <c r="E126" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F126" s="25"/>
       <c r="G126" s="5"/>
@@ -5220,7 +5213,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="18"/>
       <c r="K126" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="26.25">
@@ -5231,23 +5224,23 @@
         <v>11</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="18"/>
       <c r="K127" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="26.25">
@@ -5258,23 +5251,23 @@
         <v>11</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="18"/>
       <c r="K128" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="26.25">
@@ -5285,23 +5278,23 @@
         <v>11</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="18"/>
       <c r="K129" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5312,11 +5305,11 @@
         <v>57</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D130" s="25"/>
       <c r="E130" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F130" s="25"/>
       <c r="G130" s="5"/>
@@ -5324,7 +5317,7 @@
       <c r="I130" s="5"/>
       <c r="J130" s="18"/>
       <c r="K130" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="26.25">
@@ -5335,13 +5328,13 @@
         <v>11</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F131" s="25"/>
       <c r="G131" s="5"/>
@@ -5349,41 +5342,39 @@
       <c r="I131" s="5"/>
       <c r="J131" s="18"/>
       <c r="K131" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="13">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C132" s="9" t="s">
         <v>110</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
-      <c r="J132" s="18" t="s">
-        <v>291</v>
-      </c>
+      <c r="J132" s="18"/>
       <c r="K132" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="13">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>18</v>
@@ -5392,10 +5383,10 @@
         <v>111</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>109</v>
@@ -5408,24 +5399,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" ht="39">
       <c r="A134" s="13">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C134" s="9" t="s">
         <v>112</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -5435,48 +5426,46 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="39">
+    <row r="135" spans="1:11" ht="26.25">
       <c r="A135" s="13">
-        <v>134</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>11</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B135" s="6"/>
       <c r="C135" s="9" t="s">
         <v>113</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F135" s="9" t="s">
-        <v>113</v>
-      </c>
+      <c r="F135" s="25"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="18"/>
-      <c r="K135" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="K135" s="5"/>
     </row>
     <row r="136" spans="1:11" ht="26.25">
       <c r="A136" s="13">
-        <v>135</v>
-      </c>
-      <c r="B136" s="6"/>
+        <v>136</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C136" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F136" s="25"/>
+      <c r="F136" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -5485,7 +5474,7 @@
     </row>
     <row r="137" spans="1:11" ht="26.25">
       <c r="A137" s="13">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>18</v>
@@ -5494,13 +5483,13 @@
         <v>115</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>116</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -5510,7 +5499,7 @@
     </row>
     <row r="138" spans="1:11" ht="26.25">
       <c r="A138" s="13">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>18</v>
@@ -5519,13 +5508,13 @@
         <v>116</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>117</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -5535,7 +5524,7 @@
     </row>
     <row r="139" spans="1:11" ht="26.25">
       <c r="A139" s="13">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>18</v>
@@ -5544,13 +5533,13 @@
         <v>117</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>118</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -5560,7 +5549,7 @@
     </row>
     <row r="140" spans="1:11" ht="26.25">
       <c r="A140" s="13">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>18</v>
@@ -5569,13 +5558,13 @@
         <v>118</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>119</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -5585,7 +5574,7 @@
     </row>
     <row r="141" spans="1:11" ht="26.25">
       <c r="A141" s="13">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>18</v>
@@ -5594,13 +5583,13 @@
         <v>119</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F141" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -5610,7 +5599,7 @@
     </row>
     <row r="142" spans="1:11" ht="26.25">
       <c r="A142" s="13">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>18</v>
@@ -5619,13 +5608,13 @@
         <v>120</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>121</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -5635,7 +5624,7 @@
     </row>
     <row r="143" spans="1:11" ht="26.25">
       <c r="A143" s="13">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>18</v>
@@ -5644,13 +5633,13 @@
         <v>121</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>122</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -5660,7 +5649,7 @@
     </row>
     <row r="144" spans="1:11" ht="26.25">
       <c r="A144" s="13">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>18</v>
@@ -5669,13 +5658,13 @@
         <v>122</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>123</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -5685,7 +5674,7 @@
     </row>
     <row r="145" spans="1:11" ht="26.25">
       <c r="A145" s="13">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>18</v>
@@ -5694,13 +5683,13 @@
         <v>123</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>124</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -5708,24 +5697,22 @@
       <c r="J145" s="18"/>
       <c r="K145" s="5"/>
     </row>
-    <row r="146" spans="1:11" ht="26.25">
+    <row r="146" spans="1:11">
       <c r="A146" s="13">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D146" s="9" t="s">
         <v>114</v>
       </c>
+      <c r="D146" s="25"/>
       <c r="E146" s="9" t="s">
         <v>125</v>
       </c>
       <c r="F146" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -5735,7 +5722,7 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="13">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>11</v>
@@ -5748,7 +5735,7 @@
         <v>126</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
@@ -5758,7 +5745,7 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="13">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>11</v>
@@ -5771,7 +5758,7 @@
         <v>127</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
@@ -5781,7 +5768,7 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="13">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>11</v>
@@ -5794,7 +5781,7 @@
         <v>128</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
@@ -5804,7 +5791,7 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="13">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>11</v>
@@ -5817,7 +5804,7 @@
         <v>129</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
@@ -5827,7 +5814,7 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="13">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>11</v>
@@ -5840,7 +5827,7 @@
         <v>130</v>
       </c>
       <c r="F151" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
@@ -5850,7 +5837,7 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="13">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>11</v>
@@ -5863,7 +5850,7 @@
         <v>131</v>
       </c>
       <c r="F152" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
@@ -5873,7 +5860,7 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="13">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>11</v>
@@ -5886,7 +5873,7 @@
         <v>132</v>
       </c>
       <c r="F153" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
@@ -5896,7 +5883,7 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="13">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>11</v>
@@ -5909,7 +5896,7 @@
         <v>133</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
@@ -5919,7 +5906,7 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="13">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>11</v>
@@ -5932,7 +5919,7 @@
         <v>134</v>
       </c>
       <c r="F155" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
@@ -5942,7 +5929,7 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="13">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>11</v>
@@ -5955,7 +5942,7 @@
         <v>135</v>
       </c>
       <c r="F156" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
@@ -5963,9 +5950,9 @@
       <c r="J156" s="18"/>
       <c r="K156" s="5"/>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" ht="26.25">
       <c r="A157" s="13">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>11</v>
@@ -5973,12 +5960,14 @@
       <c r="C157" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D157" s="25"/>
+      <c r="D157" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="E157" s="9" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="F157" s="9" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
@@ -5988,7 +5977,7 @@
     </row>
     <row r="158" spans="1:11" ht="26.25">
       <c r="A158" s="13">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>11</v>
@@ -5997,7 +5986,7 @@
         <v>126</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E158" s="9" t="s">
         <v>234</v>
@@ -6013,7 +6002,7 @@
     </row>
     <row r="159" spans="1:11" ht="26.25">
       <c r="A159" s="13">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>11</v>
@@ -6022,7 +6011,7 @@
         <v>127</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>235</v>
@@ -6038,7 +6027,7 @@
     </row>
     <row r="160" spans="1:11" ht="26.25">
       <c r="A160" s="13">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>11</v>
@@ -6047,7 +6036,7 @@
         <v>128</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E160" s="9" t="s">
         <v>236</v>
@@ -6063,7 +6052,7 @@
     </row>
     <row r="161" spans="1:11" ht="26.25">
       <c r="A161" s="13">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>11</v>
@@ -6072,7 +6061,7 @@
         <v>129</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>237</v>
@@ -6088,7 +6077,7 @@
     </row>
     <row r="162" spans="1:11" ht="26.25">
       <c r="A162" s="13">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>11</v>
@@ -6097,7 +6086,7 @@
         <v>130</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E162" s="9" t="s">
         <v>238</v>
@@ -6113,7 +6102,7 @@
     </row>
     <row r="163" spans="1:11" ht="26.25">
       <c r="A163" s="13">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>11</v>
@@ -6122,7 +6111,7 @@
         <v>131</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>239</v>
@@ -6138,7 +6127,7 @@
     </row>
     <row r="164" spans="1:11" ht="26.25">
       <c r="A164" s="13">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>11</v>
@@ -6147,7 +6136,7 @@
         <v>132</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>240</v>
@@ -6163,7 +6152,7 @@
     </row>
     <row r="165" spans="1:11" ht="26.25">
       <c r="A165" s="13">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>11</v>
@@ -6172,7 +6161,7 @@
         <v>133</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>241</v>
@@ -6188,7 +6177,7 @@
     </row>
     <row r="166" spans="1:11" ht="26.25">
       <c r="A166" s="13">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>11</v>
@@ -6197,7 +6186,7 @@
         <v>134</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E166" s="9" t="s">
         <v>242</v>
@@ -6213,7 +6202,7 @@
     </row>
     <row r="167" spans="1:11" ht="26.25">
       <c r="A167" s="13">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>11</v>
@@ -6222,7 +6211,7 @@
         <v>135</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>243</v>
@@ -6236,9 +6225,9 @@
       <c r="J167" s="18"/>
       <c r="K167" s="5"/>
     </row>
-    <row r="168" spans="1:11" ht="26.25">
+    <row r="168" spans="1:11" ht="39">
       <c r="A168" s="13">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>11</v>
@@ -6259,11 +6248,13 @@
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="18"/>
-      <c r="K168" s="5"/>
-    </row>
-    <row r="169" spans="1:11" ht="39">
+      <c r="K168" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="26.25">
       <c r="A169" s="13">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>11</v>
@@ -6288,21 +6279,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="26.25">
+    <row r="170" spans="1:11">
       <c r="A170" s="13">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C170" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D170" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E170" s="9" t="s">
-        <v>246</v>
+      <c r="D170" s="25"/>
+      <c r="E170" s="26" t="s">
+        <v>333</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>138</v>
@@ -6317,7 +6306,7 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="13">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>57</v>
@@ -6327,7 +6316,7 @@
       </c>
       <c r="D171" s="25"/>
       <c r="E171" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>139</v>
@@ -6340,19 +6329,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" ht="26.25">
       <c r="A172" s="13">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C172" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D172" s="25"/>
-      <c r="E172" s="26" t="s">
-        <v>336</v>
+      <c r="D172" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>140</v>
@@ -6367,7 +6358,7 @@
     </row>
     <row r="173" spans="1:11" ht="26.25">
       <c r="A173" s="13">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>11</v>
@@ -6394,7 +6385,7 @@
     </row>
     <row r="174" spans="1:11" ht="26.25">
       <c r="A174" s="13">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>11</v>
@@ -6419,9 +6410,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="26.25">
+    <row r="175" spans="1:11" ht="39">
       <c r="A175" s="13">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>11</v>
@@ -6446,9 +6437,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="39">
+    <row r="176" spans="1:11">
       <c r="A176" s="13">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>11</v>
@@ -6473,9 +6464,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" ht="26.25">
       <c r="A177" s="13">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>11</v>
@@ -6500,9 +6491,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="26.25">
+    <row r="178" spans="1:11" ht="39">
       <c r="A178" s="13">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>11</v>
@@ -6527,9 +6518,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="39">
+    <row r="179" spans="1:11" ht="26.25">
       <c r="A179" s="13">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>11</v>
@@ -6554,21 +6545,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="26.25">
+    <row r="180" spans="1:11">
       <c r="A180" s="13">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C180" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D180" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>254</v>
+      <c r="D180" s="25"/>
+      <c r="E180" s="26" t="s">
+        <v>335</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>148</v>
@@ -6583,7 +6572,7 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="13">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>57</v>
@@ -6593,7 +6582,7 @@
       </c>
       <c r="D181" s="25"/>
       <c r="E181" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>149</v>
@@ -6608,17 +6597,19 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="13">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C182" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D182" s="25"/>
-      <c r="E182" s="26" t="s">
-        <v>338</v>
+      <c r="D182" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>254</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>150</v>
@@ -6631,9 +6622,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" ht="26.25">
       <c r="A183" s="13">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>11</v>
@@ -6642,7 +6633,7 @@
         <v>151</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>255</v>
@@ -6660,7 +6651,7 @@
     </row>
     <row r="184" spans="1:11" ht="26.25">
       <c r="A184" s="13">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>11</v>
@@ -6685,9 +6676,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="26.25">
+    <row r="185" spans="1:11" ht="39">
       <c r="A185" s="13">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>11</v>
@@ -6712,9 +6703,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="39">
+    <row r="186" spans="1:11" ht="26.25">
       <c r="A186" s="13">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>11</v>
@@ -6739,9 +6730,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="26.25">
+    <row r="187" spans="1:11">
       <c r="A187" s="13">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>11</v>
@@ -6750,7 +6741,7 @@
         <v>155</v>
       </c>
       <c r="D187" s="9" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>259</v>
@@ -6768,48 +6759,48 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="13">
-        <v>187</v>
-      </c>
-      <c r="B188" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D188" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="E188" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="F188" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
+        <v>349</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F188" s="11"/>
+      <c r="G188" s="5">
+        <v>63</v>
+      </c>
+      <c r="H188" s="5">
+        <v>15</v>
+      </c>
       <c r="I188" s="5"/>
-      <c r="J188" s="18"/>
-      <c r="K188" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="J188" s="8"/>
+      <c r="K188" s="5"/>
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="13">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B189" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="F189" s="11"/>
+        <v>359</v>
+      </c>
+      <c r="F189" s="8"/>
       <c r="G189" s="5">
         <v>63</v>
       </c>
@@ -6818,23 +6809,25 @@
       </c>
       <c r="I189" s="5"/>
       <c r="J189" s="8"/>
-      <c r="K189" s="5"/>
+      <c r="K189" s="5" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="13">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B190" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="5">
@@ -6846,24 +6839,24 @@
       <c r="I190" s="5"/>
       <c r="J190" s="8"/>
       <c r="K190" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="13">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F191" s="8"/>
       <c r="G191" s="5">
@@ -6875,24 +6868,24 @@
       <c r="I191" s="5"/>
       <c r="J191" s="8"/>
       <c r="K191" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="13">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="5">
@@ -6904,24 +6897,24 @@
       <c r="I192" s="5"/>
       <c r="J192" s="8"/>
       <c r="K192" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="13">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F193" s="8"/>
       <c r="G193" s="5">
@@ -6933,24 +6926,24 @@
       <c r="I193" s="5"/>
       <c r="J193" s="8"/>
       <c r="K193" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="13">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="5">
@@ -6962,24 +6955,24 @@
       <c r="I194" s="5"/>
       <c r="J194" s="8"/>
       <c r="K194" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="13">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B195" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F195" s="8"/>
       <c r="G195" s="5">
@@ -6991,24 +6984,24 @@
       <c r="I195" s="5"/>
       <c r="J195" s="8"/>
       <c r="K195" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="13">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B196" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="5">
@@ -7020,24 +7013,24 @@
       <c r="I196" s="5"/>
       <c r="J196" s="8"/>
       <c r="K196" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="13">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B197" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F197" s="8"/>
       <c r="G197" s="5">
@@ -7049,24 +7042,24 @@
       <c r="I197" s="5"/>
       <c r="J197" s="8"/>
       <c r="K197" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="13">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C198" s="9" t="s">
-        <v>340</v>
+      <c r="C198" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="5">
@@ -7078,24 +7071,24 @@
       <c r="I198" s="5"/>
       <c r="J198" s="8"/>
       <c r="K198" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="13">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B199" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F199" s="8"/>
       <c r="G199" s="5">
@@ -7106,11 +7099,13 @@
       </c>
       <c r="I199" s="5"/>
       <c r="J199" s="8"/>
-      <c r="K199" s="5"/>
+      <c r="K199" s="5" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="13">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>11</v>
@@ -7119,10 +7114,10 @@
         <v>341</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="5">
@@ -7134,12 +7129,12 @@
       <c r="I200" s="5"/>
       <c r="J200" s="8"/>
       <c r="K200" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="13">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>11</v>
@@ -7148,10 +7143,10 @@
         <v>342</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F201" s="8"/>
       <c r="G201" s="5">
@@ -7163,12 +7158,12 @@
       <c r="I201" s="5"/>
       <c r="J201" s="8"/>
       <c r="K201" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="13">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>11</v>
@@ -7177,10 +7172,10 @@
         <v>343</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F202" s="8"/>
       <c r="G202" s="5">
@@ -7192,12 +7187,12 @@
       <c r="I202" s="5"/>
       <c r="J202" s="8"/>
       <c r="K202" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="13">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>11</v>
@@ -7206,10 +7201,10 @@
         <v>344</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F203" s="8"/>
       <c r="G203" s="5">
@@ -7221,12 +7216,12 @@
       <c r="I203" s="5"/>
       <c r="J203" s="8"/>
       <c r="K203" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="13">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>11</v>
@@ -7235,10 +7230,10 @@
         <v>345</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="F204" s="8"/>
       <c r="G204" s="5">
@@ -7250,12 +7245,12 @@
       <c r="I204" s="5"/>
       <c r="J204" s="8"/>
       <c r="K204" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="13">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>11</v>
@@ -7264,10 +7259,10 @@
         <v>346</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F205" s="8"/>
       <c r="G205" s="5">
@@ -7279,12 +7274,12 @@
       <c r="I205" s="5"/>
       <c r="J205" s="8"/>
       <c r="K205" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="206" spans="1:11">
       <c r="A206" s="13">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>11</v>
@@ -7293,10 +7288,10 @@
         <v>347</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F206" s="8"/>
       <c r="G206" s="5">
@@ -7308,12 +7303,12 @@
       <c r="I206" s="5"/>
       <c r="J206" s="8"/>
       <c r="K206" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="13">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>11</v>
@@ -7322,10 +7317,10 @@
         <v>348</v>
       </c>
       <c r="D207" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F207" s="8"/>
       <c r="G207" s="5">
@@ -7337,68 +7332,26 @@
       <c r="I207" s="5"/>
       <c r="J207" s="8"/>
       <c r="K207" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="208" spans="1:11">
-      <c r="A208" s="13">
-        <v>207</v>
-      </c>
-      <c r="B208" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C208" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D208" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="E208" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="F208" s="8"/>
-      <c r="G208" s="5">
-        <v>63</v>
-      </c>
-      <c r="H208" s="5">
-        <v>15</v>
-      </c>
-      <c r="I208" s="5"/>
-      <c r="J208" s="8"/>
-      <c r="K208" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="209" spans="1:11">
-      <c r="A209" s="13">
-        <v>208</v>
-      </c>
-      <c r="B209" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C209" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="D209" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="E209" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="F209" s="8"/>
-      <c r="G209" s="5">
-        <v>63</v>
-      </c>
-      <c r="H209" s="5">
-        <v>15</v>
-      </c>
-      <c r="I209" s="5"/>
-      <c r="J209" s="8"/>
-      <c r="K209" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="210" spans="1:11">
+      <c r="B208" s="1"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="1"/>
+      <c r="J208" s="1"/>
+    </row>
+    <row r="209" spans="2:10">
+      <c r="B209" s="1"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
+      <c r="F209" s="1"/>
+      <c r="J209" s="1"/>
+    </row>
+    <row r="210" spans="2:10">
       <c r="B210" s="1"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -7406,7 +7359,7 @@
       <c r="F210" s="1"/>
       <c r="J210" s="1"/>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="2:10">
       <c r="B211" s="1"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
@@ -7414,7 +7367,7 @@
       <c r="F211" s="1"/>
       <c r="J211" s="1"/>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="2:10">
       <c r="B212" s="1"/>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
@@ -7422,7 +7375,7 @@
       <c r="F212" s="1"/>
       <c r="J212" s="1"/>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="2:10">
       <c r="B213" s="1"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
@@ -7430,7 +7383,7 @@
       <c r="F213" s="1"/>
       <c r="J213" s="1"/>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="2:10">
       <c r="B214" s="1"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
@@ -7438,7 +7391,7 @@
       <c r="F214" s="1"/>
       <c r="J214" s="1"/>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="2:10">
       <c r="B215" s="1"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -7446,7 +7399,7 @@
       <c r="F215" s="1"/>
       <c r="J215" s="1"/>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="2:10">
       <c r="B216" s="1"/>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
@@ -7454,7 +7407,7 @@
       <c r="F216" s="1"/>
       <c r="J216" s="1"/>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="2:10">
       <c r="B217" s="1"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
@@ -7462,7 +7415,7 @@
       <c r="F217" s="1"/>
       <c r="J217" s="1"/>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="2:10">
       <c r="B218" s="1"/>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
@@ -7470,7 +7423,7 @@
       <c r="F218" s="1"/>
       <c r="J218" s="1"/>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="2:10">
       <c r="B219" s="1"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
@@ -7478,7 +7431,7 @@
       <c r="F219" s="1"/>
       <c r="J219" s="1"/>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="2:10">
       <c r="B220" s="1"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
@@ -7486,7 +7439,7 @@
       <c r="F220" s="1"/>
       <c r="J220" s="1"/>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="2:10">
       <c r="B221" s="1"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
@@ -7494,7 +7447,7 @@
       <c r="F221" s="1"/>
       <c r="J221" s="1"/>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="2:10">
       <c r="B222" s="1"/>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
@@ -7502,7 +7455,7 @@
       <c r="F222" s="1"/>
       <c r="J222" s="1"/>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="2:10">
       <c r="B223" s="1"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
@@ -7510,7 +7463,7 @@
       <c r="F223" s="1"/>
       <c r="J223" s="1"/>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="2:10">
       <c r="B224" s="1"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -13590,24 +13543,8 @@
       <c r="F983" s="1"/>
       <c r="J983" s="1"/>
     </row>
-    <row r="984" spans="2:10">
-      <c r="B984" s="1"/>
-      <c r="C984" s="3"/>
-      <c r="D984" s="3"/>
-      <c r="E984" s="3"/>
-      <c r="F984" s="1"/>
-      <c r="J984" s="1"/>
-    </row>
-    <row r="985" spans="2:10">
-      <c r="B985" s="1"/>
-      <c r="C985" s="3"/>
-      <c r="D985" s="3"/>
-      <c r="E985" s="3"/>
-      <c r="F985" s="1"/>
-      <c r="J985" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K209" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K207" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -13634,30 +13571,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E2" s="4">
         <v>0.5</v>
@@ -13665,16 +13602,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E3" s="4">
         <v>0.3</v>
@@ -13700,104 +13637,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -13819,104 +13756,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/download/input.xlsx
+++ b/download/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBE94AF-2BDD-433E-9A3C-FCC319DC2256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ACD2A2-439E-4B4B-8644-0147C88EB27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="379">
   <si>
     <t>id</t>
   </si>
@@ -925,9 +925,6 @@
     <t>Узел 1QF 1 с.ш. ГРЩ1/QS1 1 с.ш. ППУ ГРЩ1</t>
   </si>
   <si>
-    <t>Учет Pi 1 с.ш. ГРЩ1</t>
-  </si>
-  <si>
     <t>Учет Pqs1 ППУ</t>
   </si>
   <si>
@@ -940,9 +937,6 @@
     <t>Узел QF2 1 с.ш. ППУ/ QF5 2 с.ш. ППУ</t>
   </si>
   <si>
-    <t>Узуч 1 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
-  </si>
-  <si>
     <t>Узел QF3 2 с.ш. ГРЩ1/ Узел QF3 1 с.ш. ППУ/QF6 2 с.ш. ППУ ГРЩ1</t>
   </si>
   <si>
@@ -1172,6 +1166,9 @@
   </si>
   <si>
     <t>Учет 2 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
+  </si>
+  <si>
+    <t>Учет Pi 1 с.ш. ART-03 PQRS, 5(10)A 5000/5  ГРЩ1</t>
   </si>
 </sst>
 </file>
@@ -1724,6 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K983"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
@@ -1775,7 +1773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" hidden="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1808,7 +1806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" hidden="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1841,7 +1839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26.25">
+    <row r="4" spans="1:11" ht="26.25" hidden="1">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -1871,10 +1869,10 @@
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" hidden="1">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -1907,7 +1905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.25">
+    <row r="6" spans="1:11" ht="26.25" hidden="1">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -1940,7 +1938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" ht="30" hidden="1">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -1954,7 +1952,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="5">
@@ -1966,86 +1964,82 @@
       <c r="I7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="6"/>
+      <c r="J7" s="19" t="s">
+        <v>330</v>
+      </c>
       <c r="K7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="13">
-        <v>7</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>11</v>
-      </c>
+    <row r="8" spans="1:11" ht="26.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="15" t="s">
-        <v>60</v>
+        <v>378</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="5">
         <v>16</v>
       </c>
-      <c r="H8" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="6"/>
       <c r="K8" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="26.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" hidden="1">
       <c r="A9" s="13">
-        <v>8</v>
-      </c>
-      <c r="B9" s="17"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>11</v>
+      </c>
       <c r="C9" s="15" t="s">
-        <v>298</v>
+        <v>60</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+        <v>297</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="5">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="J9" s="6"/>
       <c r="K9" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="26.25">
+    <row r="10" spans="1:11" ht="26.25" hidden="1">
       <c r="A10" s="13">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>18</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B10" s="17"/>
       <c r="C10" s="15" t="s">
-        <v>61</v>
+        <v>297</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>59</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F10" s="16"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -2054,9 +2048,9 @@
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="26.25">
+    <row r="11" spans="1:11" ht="26.25" hidden="1">
       <c r="A11" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>18</v>
@@ -2068,7 +2062,7 @@
         <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>59</v>
@@ -2081,48 +2075,48 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="26.25">
+    <row r="12" spans="1:11" ht="26.25" hidden="1">
       <c r="A12" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
       <c r="K12" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="26.25" hidden="1">
       <c r="A13" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>299</v>
+        <v>62</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>109</v>
+        <v>298</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>62</v>
@@ -2132,24 +2126,24 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="26.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" hidden="1">
       <c r="A14" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>62</v>
@@ -2157,26 +2151,26 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="18"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="26.25" hidden="1">
       <c r="A15" s="13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C15" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>63</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>300</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>62</v>
@@ -2184,55 +2178,55 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="18" t="s">
-        <v>289</v>
-      </c>
+      <c r="J15" s="18"/>
       <c r="K15" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" ht="30" hidden="1">
       <c r="A16" s="13">
-        <v>15</v>
-      </c>
-      <c r="B16" s="17"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>11</v>
+      </c>
       <c r="C16" s="15" t="s">
-        <v>300</v>
+        <v>63</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="F16" s="16"/>
+        <v>299</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="18" t="s">
+        <v>289</v>
+      </c>
       <c r="K16" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" s="13">
-        <v>16</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B17" s="17"/>
       <c r="C17" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>62</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="F17" s="16"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2241,21 +2235,21 @@
         <v>294</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" hidden="1">
       <c r="A18" s="13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>62</v>
@@ -2268,53 +2262,51 @@
         <v>294</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="30">
+    <row r="19" spans="1:11" hidden="1">
       <c r="A19" s="13">
+        <v>17</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>57</v>
-      </c>
       <c r="C19" s="15" t="s">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="18" t="s">
-        <v>289</v>
-      </c>
+      <c r="J19" s="6"/>
       <c r="K19" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="30">
+    <row r="20" spans="1:11" ht="30" hidden="1">
       <c r="A20" s="13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>57</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -2326,15 +2318,15 @@
         <v>294</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="30" hidden="1">
       <c r="A21" s="13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>159</v>
@@ -2343,46 +2335,48 @@
         <v>75</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="6" t="s">
-        <v>290</v>
+      <c r="J21" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" hidden="1">
       <c r="A22" s="13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="F22" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>67</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="19" t="s">
-        <v>332</v>
+      <c r="J22" s="6" t="s">
+        <v>290</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="26.25">
+    <row r="23" spans="1:11" ht="26.25" hidden="1">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -2396,7 +2390,7 @@
         <v>159</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>62</v>
@@ -2411,7 +2405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="25.5">
+    <row r="24" spans="1:11" ht="25.5" hidden="1">
       <c r="A24" s="13">
         <v>23</v>
       </c>
@@ -2425,7 +2419,7 @@
         <v>162</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>262</v>
@@ -2435,16 +2429,16 @@
       <c r="I24" s="5"/>
       <c r="J24" s="22"/>
       <c r="K24" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="25.5">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="25.5" hidden="1">
       <c r="A25" s="13">
         <v>24</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>159</v>
@@ -2461,7 +2455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" hidden="1">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -2486,19 +2480,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="25.5">
+    <row r="27" spans="1:11" ht="25.5" hidden="1">
       <c r="A27" s="13">
         <v>26</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="5"/>
@@ -2509,13 +2503,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" hidden="1">
       <c r="A28" s="13">
         <v>27</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>159</v>
@@ -2532,7 +2526,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" hidden="1">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -2557,13 +2551,13 @@
         <v>294</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" hidden="1">
       <c r="A30" s="13">
         <v>29</v>
       </c>
       <c r="B30" s="23"/>
       <c r="C30" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>159</v>
@@ -2580,7 +2574,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" hidden="1">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -2605,7 +2599,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="30">
+    <row r="32" spans="1:11" ht="30" hidden="1">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -2634,7 +2628,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="30">
+    <row r="33" spans="1:11" ht="30" hidden="1">
       <c r="A33" s="13">
         <v>32</v>
       </c>
@@ -2663,7 +2657,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="30">
+    <row r="34" spans="1:11" ht="30" hidden="1">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -2692,7 +2686,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="26.25">
+    <row r="35" spans="1:11" ht="26.25" hidden="1">
       <c r="A35" s="13">
         <v>34</v>
       </c>
@@ -2706,7 +2700,7 @@
         <v>159</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>265</v>
@@ -2719,7 +2713,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="26.25">
+    <row r="36" spans="1:11" ht="26.25" hidden="1">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -2733,7 +2727,7 @@
         <v>159</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>265</v>
@@ -2746,7 +2740,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="26.25">
+    <row r="37" spans="1:11" ht="26.25" hidden="1">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -2760,7 +2754,7 @@
         <v>159</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>265</v>
@@ -2773,7 +2767,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="26.25">
+    <row r="38" spans="1:11" ht="26.25" hidden="1">
       <c r="A38" s="13">
         <v>37</v>
       </c>
@@ -2787,7 +2781,7 @@
         <v>159</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>265</v>
@@ -2800,7 +2794,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="26.25">
+    <row r="39" spans="1:11" ht="26.25" hidden="1">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -2814,7 +2808,7 @@
         <v>159</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>265</v>
@@ -2827,7 +2821,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="26.25">
+    <row r="40" spans="1:11" ht="26.25" hidden="1">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -2841,7 +2835,7 @@
         <v>159</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>265</v>
@@ -2854,7 +2848,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="26.25">
+    <row r="41" spans="1:11" ht="26.25" hidden="1">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -2868,7 +2862,7 @@
         <v>159</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>265</v>
@@ -2881,7 +2875,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="26.25">
+    <row r="42" spans="1:11" ht="26.25" hidden="1">
       <c r="A42" s="13">
         <v>41</v>
       </c>
@@ -2895,7 +2889,7 @@
         <v>159</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>265</v>
@@ -2908,7 +2902,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="26.25">
+    <row r="43" spans="1:11" ht="26.25" hidden="1">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -2922,7 +2916,7 @@
         <v>159</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F43" s="24" t="s">
         <v>266</v>
@@ -2935,7 +2929,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="26.25">
+    <row r="44" spans="1:11" ht="26.25" hidden="1">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -2949,7 +2943,7 @@
         <v>159</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F44" s="24" t="s">
         <v>266</v>
@@ -2962,7 +2956,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="26.25">
+    <row r="45" spans="1:11" ht="26.25" hidden="1">
       <c r="A45" s="13">
         <v>44</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>159</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F45" s="24" t="s">
         <v>266</v>
@@ -2989,7 +2983,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="51.75">
+    <row r="46" spans="1:11" ht="51.75" hidden="1">
       <c r="A46" s="13">
         <v>45</v>
       </c>
@@ -3016,7 +3010,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="26.25">
+    <row r="47" spans="1:11" ht="26.25" hidden="1">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -3030,7 +3024,7 @@
         <v>159</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>266</v>
@@ -3043,7 +3037,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="26.25">
+    <row r="48" spans="1:11" ht="26.25" hidden="1">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -3057,7 +3051,7 @@
         <v>159</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>266</v>
@@ -3070,7 +3064,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="26.25">
+    <row r="49" spans="1:11" ht="26.25" hidden="1">
       <c r="A49" s="13">
         <v>48</v>
       </c>
@@ -3084,7 +3078,7 @@
         <v>159</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>266</v>
@@ -3097,7 +3091,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="26.25">
+    <row r="50" spans="1:11" ht="26.25" hidden="1">
       <c r="A50" s="13">
         <v>49</v>
       </c>
@@ -3111,7 +3105,7 @@
         <v>159</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>266</v>
@@ -3124,7 +3118,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="26.25">
+    <row r="51" spans="1:11" ht="26.25" hidden="1">
       <c r="A51" s="13">
         <v>50</v>
       </c>
@@ -3138,7 +3132,7 @@
         <v>159</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>266</v>
@@ -3151,7 +3145,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="26.25">
+    <row r="52" spans="1:11" ht="26.25" hidden="1">
       <c r="A52" s="13">
         <v>51</v>
       </c>
@@ -3165,7 +3159,7 @@
         <v>159</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>266</v>
@@ -3178,7 +3172,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="26.25">
+    <row r="53" spans="1:11" ht="26.25" hidden="1">
       <c r="A53" s="13">
         <v>52</v>
       </c>
@@ -3192,7 +3186,7 @@
         <v>159</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>266</v>
@@ -3205,7 +3199,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="26.25">
+    <row r="54" spans="1:11" ht="26.25" hidden="1">
       <c r="A54" s="13">
         <v>53</v>
       </c>
@@ -3219,7 +3213,7 @@
         <v>159</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>266</v>
@@ -3232,7 +3226,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="26.25">
+    <row r="55" spans="1:11" ht="26.25" hidden="1">
       <c r="A55" s="13">
         <v>54</v>
       </c>
@@ -3246,7 +3240,7 @@
         <v>159</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>266</v>
@@ -3259,7 +3253,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="26.25">
+    <row r="56" spans="1:11" ht="26.25" hidden="1">
       <c r="A56" s="13">
         <v>55</v>
       </c>
@@ -3273,7 +3267,7 @@
         <v>159</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>266</v>
@@ -3286,7 +3280,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="26.25">
+    <row r="57" spans="1:11" ht="26.25" hidden="1">
       <c r="A57" s="13">
         <v>56</v>
       </c>
@@ -3315,7 +3309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" hidden="1">
       <c r="A58" s="13">
         <v>57</v>
       </c>
@@ -3344,7 +3338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" hidden="1">
       <c r="A59" s="13">
         <v>58</v>
       </c>
@@ -3373,7 +3367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" hidden="1">
       <c r="A60" s="13">
         <v>59</v>
       </c>
@@ -3402,7 +3396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" hidden="1">
       <c r="A61" s="13">
         <v>60</v>
       </c>
@@ -3431,7 +3425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" hidden="1">
       <c r="A62" s="13">
         <v>61</v>
       </c>
@@ -3460,7 +3454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" hidden="1">
       <c r="A63" s="13">
         <v>62</v>
       </c>
@@ -3489,7 +3483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" hidden="1">
       <c r="A64" s="13">
         <v>63</v>
       </c>
@@ -3518,7 +3512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" hidden="1">
       <c r="A65" s="13">
         <v>64</v>
       </c>
@@ -3547,7 +3541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" hidden="1">
       <c r="A66" s="13">
         <v>65</v>
       </c>
@@ -3576,7 +3570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" hidden="1">
       <c r="A67" s="13">
         <v>66</v>
       </c>
@@ -3605,7 +3599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" hidden="1">
       <c r="A68" s="13">
         <v>67</v>
       </c>
@@ -3634,7 +3628,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" hidden="1">
       <c r="A69" s="13">
         <v>68</v>
       </c>
@@ -3663,7 +3657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" hidden="1">
       <c r="A70" s="13">
         <v>69</v>
       </c>
@@ -3692,7 +3686,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" hidden="1">
       <c r="A71" s="13">
         <v>70</v>
       </c>
@@ -3721,7 +3715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" hidden="1">
       <c r="A72" s="13">
         <v>71</v>
       </c>
@@ -3750,7 +3744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" s="13">
         <v>72</v>
       </c>
@@ -3779,7 +3773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" s="13">
         <v>73</v>
       </c>
@@ -3808,7 +3802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" hidden="1">
       <c r="A75" s="13">
         <v>74</v>
       </c>
@@ -3837,7 +3831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" s="13">
         <v>75</v>
       </c>
@@ -3866,7 +3860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" hidden="1">
       <c r="A77" s="13">
         <v>76</v>
       </c>
@@ -3895,7 +3889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="26.25">
+    <row r="78" spans="1:11" ht="26.25" hidden="1">
       <c r="A78" s="13">
         <v>77</v>
       </c>
@@ -3924,7 +3918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="26.25">
+    <row r="79" spans="1:11" ht="26.25" hidden="1">
       <c r="A79" s="13">
         <v>78</v>
       </c>
@@ -3951,7 +3945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" hidden="1">
       <c r="A80" s="13">
         <v>79</v>
       </c>
@@ -3978,7 +3972,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="64.5">
+    <row r="81" spans="1:11" ht="64.5" hidden="1">
       <c r="A81" s="13">
         <v>80</v>
       </c>
@@ -3986,7 +3980,7 @@
         <v>57</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>164</v>
@@ -4005,7 +3999,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" hidden="1">
       <c r="A82" s="13">
         <v>81</v>
       </c>
@@ -4032,7 +4026,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="13">
         <v>82</v>
       </c>
@@ -4059,7 +4053,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" hidden="1">
       <c r="A84" s="13">
         <v>83</v>
       </c>
@@ -4086,7 +4080,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" hidden="1">
       <c r="A85" s="13">
         <v>84</v>
       </c>
@@ -4113,7 +4107,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" hidden="1">
       <c r="A86" s="13">
         <v>85</v>
       </c>
@@ -4142,7 +4136,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" hidden="1">
       <c r="A87" s="13">
         <v>86</v>
       </c>
@@ -4171,7 +4165,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="26.25">
+    <row r="88" spans="1:11" ht="26.25" hidden="1">
       <c r="A88" s="13">
         <v>87</v>
       </c>
@@ -4198,7 +4192,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="26.25">
+    <row r="89" spans="1:11" ht="26.25" hidden="1">
       <c r="A89" s="13">
         <v>88</v>
       </c>
@@ -4225,7 +4219,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="26.25">
+    <row r="90" spans="1:11" ht="26.25" hidden="1">
       <c r="A90" s="13">
         <v>89</v>
       </c>
@@ -4252,7 +4246,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="26.25">
+    <row r="91" spans="1:11" ht="26.25" hidden="1">
       <c r="A91" s="13">
         <v>90</v>
       </c>
@@ -4279,7 +4273,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="26.25">
+    <row r="92" spans="1:11" ht="26.25" hidden="1">
       <c r="A92" s="13">
         <v>91</v>
       </c>
@@ -4306,7 +4300,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="26.25">
+    <row r="93" spans="1:11" ht="26.25" hidden="1">
       <c r="A93" s="13">
         <v>92</v>
       </c>
@@ -4333,7 +4327,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="26.25">
+    <row r="94" spans="1:11" ht="26.25" hidden="1">
       <c r="A94" s="13">
         <v>93</v>
       </c>
@@ -4360,7 +4354,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="26.25">
+    <row r="95" spans="1:11" ht="26.25" hidden="1">
       <c r="A95" s="13">
         <v>94</v>
       </c>
@@ -4387,7 +4381,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="26.25">
+    <row r="96" spans="1:11" ht="26.25" hidden="1">
       <c r="A96" s="13">
         <v>95</v>
       </c>
@@ -4414,7 +4408,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="26.25">
+    <row r="97" spans="1:11" ht="26.25" hidden="1">
       <c r="A97" s="13">
         <v>96</v>
       </c>
@@ -4441,7 +4435,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="26.25">
+    <row r="98" spans="1:11" ht="26.25" hidden="1">
       <c r="A98" s="13">
         <v>97</v>
       </c>
@@ -4468,7 +4462,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="26.25">
+    <row r="99" spans="1:11" ht="26.25" hidden="1">
       <c r="A99" s="13">
         <v>98</v>
       </c>
@@ -4495,7 +4489,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="26.25">
+    <row r="100" spans="1:11" ht="26.25" hidden="1">
       <c r="A100" s="13">
         <v>99</v>
       </c>
@@ -4522,7 +4516,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="26.25">
+    <row r="101" spans="1:11" ht="26.25" hidden="1">
       <c r="A101" s="13">
         <v>100</v>
       </c>
@@ -4549,7 +4543,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="26.25">
+    <row r="102" spans="1:11" ht="26.25" hidden="1">
       <c r="A102" s="13">
         <v>101</v>
       </c>
@@ -4576,7 +4570,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="26.25">
+    <row r="103" spans="1:11" ht="26.25" hidden="1">
       <c r="A103" s="13">
         <v>102</v>
       </c>
@@ -4603,7 +4597,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="26.25">
+    <row r="104" spans="1:11" ht="26.25" hidden="1">
       <c r="A104" s="13">
         <v>103</v>
       </c>
@@ -4630,7 +4624,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="26.25">
+    <row r="105" spans="1:11" ht="26.25" hidden="1">
       <c r="A105" s="13">
         <v>104</v>
       </c>
@@ -4657,7 +4651,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="26.25">
+    <row r="106" spans="1:11" ht="26.25" hidden="1">
       <c r="A106" s="13">
         <v>105</v>
       </c>
@@ -4684,7 +4678,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="26.25">
+    <row r="107" spans="1:11" ht="26.25" hidden="1">
       <c r="A107" s="13">
         <v>106</v>
       </c>
@@ -4711,7 +4705,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="26.25">
+    <row r="108" spans="1:11" ht="26.25" hidden="1">
       <c r="A108" s="13">
         <v>107</v>
       </c>
@@ -4738,7 +4732,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="26.25">
+    <row r="109" spans="1:11" ht="26.25" hidden="1">
       <c r="A109" s="13">
         <v>108</v>
       </c>
@@ -4765,7 +4759,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="26.25">
+    <row r="110" spans="1:11" ht="26.25" hidden="1">
       <c r="A110" s="13">
         <v>109</v>
       </c>
@@ -4792,7 +4786,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="26.25">
+    <row r="111" spans="1:11" ht="26.25" hidden="1">
       <c r="A111" s="13">
         <v>110</v>
       </c>
@@ -4819,7 +4813,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="26.25">
+    <row r="112" spans="1:11" ht="26.25" hidden="1">
       <c r="A112" s="13">
         <v>111</v>
       </c>
@@ -4846,7 +4840,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="26.25">
+    <row r="113" spans="1:11" ht="26.25" hidden="1">
       <c r="A113" s="13">
         <v>112</v>
       </c>
@@ -4873,7 +4867,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="26.25">
+    <row r="114" spans="1:11" ht="26.25" hidden="1">
       <c r="A114" s="13">
         <v>113</v>
       </c>
@@ -4900,7 +4894,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="26.25">
+    <row r="115" spans="1:11" ht="26.25" hidden="1">
       <c r="A115" s="13">
         <v>114</v>
       </c>
@@ -4927,7 +4921,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="26.25">
+    <row r="116" spans="1:11" ht="26.25" hidden="1">
       <c r="A116" s="13">
         <v>115</v>
       </c>
@@ -4954,7 +4948,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="26.25">
+    <row r="117" spans="1:11" ht="26.25" hidden="1">
       <c r="A117" s="13">
         <v>116</v>
       </c>
@@ -4981,7 +4975,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="26.25">
+    <row r="118" spans="1:11" ht="26.25" hidden="1">
       <c r="A118" s="13">
         <v>117</v>
       </c>
@@ -5008,7 +5002,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="26.25">
+    <row r="119" spans="1:11" ht="26.25" hidden="1">
       <c r="A119" s="13">
         <v>118</v>
       </c>
@@ -5035,7 +5029,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="39">
+    <row r="120" spans="1:11" ht="39" hidden="1">
       <c r="A120" s="13">
         <v>119</v>
       </c>
@@ -5062,7 +5056,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" hidden="1">
       <c r="A121" s="13">
         <v>120</v>
       </c>
@@ -5085,7 +5079,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="64.5">
+    <row r="122" spans="1:11" ht="64.5" hidden="1">
       <c r="A122" s="13">
         <v>121</v>
       </c>
@@ -5112,7 +5106,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="64.5">
+    <row r="123" spans="1:11" ht="64.5" hidden="1">
       <c r="A123" s="13">
         <v>122</v>
       </c>
@@ -5139,7 +5133,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="51.75">
+    <row r="124" spans="1:11" ht="51.75" hidden="1">
       <c r="A124" s="13">
         <v>123</v>
       </c>
@@ -5166,7 +5160,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="39">
+    <row r="125" spans="1:11" ht="39" hidden="1">
       <c r="A125" s="13">
         <v>124</v>
       </c>
@@ -5193,7 +5187,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" hidden="1">
       <c r="A126" s="13">
         <v>125</v>
       </c>
@@ -5216,7 +5210,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="26.25">
+    <row r="127" spans="1:11" ht="26.25" hidden="1">
       <c r="A127" s="13">
         <v>126</v>
       </c>
@@ -5243,7 +5237,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="26.25">
+    <row r="128" spans="1:11" ht="26.25" hidden="1">
       <c r="A128" s="13">
         <v>127</v>
       </c>
@@ -5270,7 +5264,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="26.25">
+    <row r="129" spans="1:11" ht="26.25" hidden="1">
       <c r="A129" s="13">
         <v>128</v>
       </c>
@@ -5297,7 +5291,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" hidden="1">
       <c r="A130" s="13">
         <v>129</v>
       </c>
@@ -5320,7 +5314,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="26.25">
+    <row r="131" spans="1:11" ht="26.25" hidden="1">
       <c r="A131" s="13">
         <v>130</v>
       </c>
@@ -5345,7 +5339,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" hidden="1">
       <c r="A132" s="13">
         <v>132</v>
       </c>
@@ -5372,7 +5366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" hidden="1">
       <c r="A133" s="13">
         <v>133</v>
       </c>
@@ -5399,7 +5393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="39">
+    <row r="134" spans="1:11" ht="39" hidden="1">
       <c r="A134" s="13">
         <v>134</v>
       </c>
@@ -5426,7 +5420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="26.25">
+    <row r="135" spans="1:11" ht="26.25" hidden="1">
       <c r="A135" s="13">
         <v>135</v>
       </c>
@@ -5447,7 +5441,7 @@
       <c r="J135" s="18"/>
       <c r="K135" s="5"/>
     </row>
-    <row r="136" spans="1:11" ht="26.25">
+    <row r="136" spans="1:11" ht="26.25" hidden="1">
       <c r="A136" s="13">
         <v>136</v>
       </c>
@@ -5472,7 +5466,7 @@
       <c r="J136" s="18"/>
       <c r="K136" s="5"/>
     </row>
-    <row r="137" spans="1:11" ht="26.25">
+    <row r="137" spans="1:11" ht="26.25" hidden="1">
       <c r="A137" s="13">
         <v>137</v>
       </c>
@@ -5497,7 +5491,7 @@
       <c r="J137" s="18"/>
       <c r="K137" s="5"/>
     </row>
-    <row r="138" spans="1:11" ht="26.25">
+    <row r="138" spans="1:11" ht="26.25" hidden="1">
       <c r="A138" s="13">
         <v>138</v>
       </c>
@@ -5522,7 +5516,7 @@
       <c r="J138" s="18"/>
       <c r="K138" s="5"/>
     </row>
-    <row r="139" spans="1:11" ht="26.25">
+    <row r="139" spans="1:11" ht="26.25" hidden="1">
       <c r="A139" s="13">
         <v>139</v>
       </c>
@@ -5547,7 +5541,7 @@
       <c r="J139" s="18"/>
       <c r="K139" s="5"/>
     </row>
-    <row r="140" spans="1:11" ht="26.25">
+    <row r="140" spans="1:11" ht="26.25" hidden="1">
       <c r="A140" s="13">
         <v>140</v>
       </c>
@@ -5572,7 +5566,7 @@
       <c r="J140" s="18"/>
       <c r="K140" s="5"/>
     </row>
-    <row r="141" spans="1:11" ht="26.25">
+    <row r="141" spans="1:11" ht="26.25" hidden="1">
       <c r="A141" s="13">
         <v>141</v>
       </c>
@@ -5597,7 +5591,7 @@
       <c r="J141" s="18"/>
       <c r="K141" s="5"/>
     </row>
-    <row r="142" spans="1:11" ht="26.25">
+    <row r="142" spans="1:11" ht="26.25" hidden="1">
       <c r="A142" s="13">
         <v>142</v>
       </c>
@@ -5622,7 +5616,7 @@
       <c r="J142" s="18"/>
       <c r="K142" s="5"/>
     </row>
-    <row r="143" spans="1:11" ht="26.25">
+    <row r="143" spans="1:11" ht="26.25" hidden="1">
       <c r="A143" s="13">
         <v>143</v>
       </c>
@@ -5647,7 +5641,7 @@
       <c r="J143" s="18"/>
       <c r="K143" s="5"/>
     </row>
-    <row r="144" spans="1:11" ht="26.25">
+    <row r="144" spans="1:11" ht="26.25" hidden="1">
       <c r="A144" s="13">
         <v>144</v>
       </c>
@@ -5672,7 +5666,7 @@
       <c r="J144" s="18"/>
       <c r="K144" s="5"/>
     </row>
-    <row r="145" spans="1:11" ht="26.25">
+    <row r="145" spans="1:11" ht="26.25" hidden="1">
       <c r="A145" s="13">
         <v>145</v>
       </c>
@@ -5697,7 +5691,7 @@
       <c r="J145" s="18"/>
       <c r="K145" s="5"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" hidden="1">
       <c r="A146" s="13">
         <v>146</v>
       </c>
@@ -5720,7 +5714,7 @@
       <c r="J146" s="18"/>
       <c r="K146" s="5"/>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" hidden="1">
       <c r="A147" s="13">
         <v>147</v>
       </c>
@@ -5743,7 +5737,7 @@
       <c r="J147" s="18"/>
       <c r="K147" s="5"/>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" hidden="1">
       <c r="A148" s="13">
         <v>148</v>
       </c>
@@ -5766,7 +5760,7 @@
       <c r="J148" s="18"/>
       <c r="K148" s="5"/>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149" s="13">
         <v>149</v>
       </c>
@@ -5789,7 +5783,7 @@
       <c r="J149" s="18"/>
       <c r="K149" s="5"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" hidden="1">
       <c r="A150" s="13">
         <v>150</v>
       </c>
@@ -5812,7 +5806,7 @@
       <c r="J150" s="18"/>
       <c r="K150" s="5"/>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" hidden="1">
       <c r="A151" s="13">
         <v>151</v>
       </c>
@@ -5835,7 +5829,7 @@
       <c r="J151" s="18"/>
       <c r="K151" s="5"/>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" hidden="1">
       <c r="A152" s="13">
         <v>152</v>
       </c>
@@ -5858,7 +5852,7 @@
       <c r="J152" s="18"/>
       <c r="K152" s="5"/>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" hidden="1">
       <c r="A153" s="13">
         <v>153</v>
       </c>
@@ -5881,7 +5875,7 @@
       <c r="J153" s="18"/>
       <c r="K153" s="5"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" hidden="1">
       <c r="A154" s="13">
         <v>154</v>
       </c>
@@ -5904,7 +5898,7 @@
       <c r="J154" s="18"/>
       <c r="K154" s="5"/>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" hidden="1">
       <c r="A155" s="13">
         <v>155</v>
       </c>
@@ -5927,7 +5921,7 @@
       <c r="J155" s="18"/>
       <c r="K155" s="5"/>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" hidden="1">
       <c r="A156" s="13">
         <v>156</v>
       </c>
@@ -5950,7 +5944,7 @@
       <c r="J156" s="18"/>
       <c r="K156" s="5"/>
     </row>
-    <row r="157" spans="1:11" ht="26.25">
+    <row r="157" spans="1:11" ht="26.25" hidden="1">
       <c r="A157" s="13">
         <v>157</v>
       </c>
@@ -5975,7 +5969,7 @@
       <c r="J157" s="18"/>
       <c r="K157" s="5"/>
     </row>
-    <row r="158" spans="1:11" ht="26.25">
+    <row r="158" spans="1:11" ht="26.25" hidden="1">
       <c r="A158" s="13">
         <v>158</v>
       </c>
@@ -6000,7 +5994,7 @@
       <c r="J158" s="18"/>
       <c r="K158" s="5"/>
     </row>
-    <row r="159" spans="1:11" ht="26.25">
+    <row r="159" spans="1:11" ht="26.25" hidden="1">
       <c r="A159" s="13">
         <v>159</v>
       </c>
@@ -6025,7 +6019,7 @@
       <c r="J159" s="18"/>
       <c r="K159" s="5"/>
     </row>
-    <row r="160" spans="1:11" ht="26.25">
+    <row r="160" spans="1:11" ht="26.25" hidden="1">
       <c r="A160" s="13">
         <v>160</v>
       </c>
@@ -6050,7 +6044,7 @@
       <c r="J160" s="18"/>
       <c r="K160" s="5"/>
     </row>
-    <row r="161" spans="1:11" ht="26.25">
+    <row r="161" spans="1:11" ht="26.25" hidden="1">
       <c r="A161" s="13">
         <v>161</v>
       </c>
@@ -6075,7 +6069,7 @@
       <c r="J161" s="18"/>
       <c r="K161" s="5"/>
     </row>
-    <row r="162" spans="1:11" ht="26.25">
+    <row r="162" spans="1:11" ht="26.25" hidden="1">
       <c r="A162" s="13">
         <v>162</v>
       </c>
@@ -6100,7 +6094,7 @@
       <c r="J162" s="18"/>
       <c r="K162" s="5"/>
     </row>
-    <row r="163" spans="1:11" ht="26.25">
+    <row r="163" spans="1:11" ht="26.25" hidden="1">
       <c r="A163" s="13">
         <v>163</v>
       </c>
@@ -6125,7 +6119,7 @@
       <c r="J163" s="18"/>
       <c r="K163" s="5"/>
     </row>
-    <row r="164" spans="1:11" ht="26.25">
+    <row r="164" spans="1:11" ht="26.25" hidden="1">
       <c r="A164" s="13">
         <v>164</v>
       </c>
@@ -6150,7 +6144,7 @@
       <c r="J164" s="18"/>
       <c r="K164" s="5"/>
     </row>
-    <row r="165" spans="1:11" ht="26.25">
+    <row r="165" spans="1:11" ht="26.25" hidden="1">
       <c r="A165" s="13">
         <v>165</v>
       </c>
@@ -6175,7 +6169,7 @@
       <c r="J165" s="18"/>
       <c r="K165" s="5"/>
     </row>
-    <row r="166" spans="1:11" ht="26.25">
+    <row r="166" spans="1:11" ht="26.25" hidden="1">
       <c r="A166" s="13">
         <v>166</v>
       </c>
@@ -6200,7 +6194,7 @@
       <c r="J166" s="18"/>
       <c r="K166" s="5"/>
     </row>
-    <row r="167" spans="1:11" ht="26.25">
+    <row r="167" spans="1:11" ht="26.25" hidden="1">
       <c r="A167" s="13">
         <v>167</v>
       </c>
@@ -6225,7 +6219,7 @@
       <c r="J167" s="18"/>
       <c r="K167" s="5"/>
     </row>
-    <row r="168" spans="1:11" ht="39">
+    <row r="168" spans="1:11" ht="39" hidden="1">
       <c r="A168" s="13">
         <v>168</v>
       </c>
@@ -6252,7 +6246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="26.25">
+    <row r="169" spans="1:11" ht="26.25" hidden="1">
       <c r="A169" s="13">
         <v>169</v>
       </c>
@@ -6279,7 +6273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170" s="13">
         <v>170</v>
       </c>
@@ -6291,7 +6285,7 @@
       </c>
       <c r="D170" s="25"/>
       <c r="E170" s="26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>138</v>
@@ -6304,7 +6298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" hidden="1">
       <c r="A171" s="13">
         <v>171</v>
       </c>
@@ -6316,7 +6310,7 @@
       </c>
       <c r="D171" s="25"/>
       <c r="E171" s="26" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>139</v>
@@ -6329,7 +6323,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="26.25">
+    <row r="172" spans="1:11" ht="26.25" hidden="1">
       <c r="A172" s="13">
         <v>172</v>
       </c>
@@ -6356,7 +6350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="26.25">
+    <row r="173" spans="1:11" ht="26.25" hidden="1">
       <c r="A173" s="13">
         <v>173</v>
       </c>
@@ -6383,7 +6377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="26.25">
+    <row r="174" spans="1:11" ht="26.25" hidden="1">
       <c r="A174" s="13">
         <v>174</v>
       </c>
@@ -6410,7 +6404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="39">
+    <row r="175" spans="1:11" ht="39" hidden="1">
       <c r="A175" s="13">
         <v>175</v>
       </c>
@@ -6437,7 +6431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176" s="13">
         <v>176</v>
       </c>
@@ -6464,7 +6458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="26.25">
+    <row r="177" spans="1:11" ht="26.25" hidden="1">
       <c r="A177" s="13">
         <v>177</v>
       </c>
@@ -6491,7 +6485,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="39">
+    <row r="178" spans="1:11" ht="39" hidden="1">
       <c r="A178" s="13">
         <v>178</v>
       </c>
@@ -6518,7 +6512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="26.25">
+    <row r="179" spans="1:11" ht="26.25" hidden="1">
       <c r="A179" s="13">
         <v>179</v>
       </c>
@@ -6545,7 +6539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" hidden="1">
       <c r="A180" s="13">
         <v>180</v>
       </c>
@@ -6557,7 +6551,7 @@
       </c>
       <c r="D180" s="25"/>
       <c r="E180" s="26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>148</v>
@@ -6570,7 +6564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181" s="13">
         <v>181</v>
       </c>
@@ -6582,7 +6576,7 @@
       </c>
       <c r="D181" s="25"/>
       <c r="E181" s="26" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>149</v>
@@ -6595,7 +6589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182" s="13">
         <v>182</v>
       </c>
@@ -6622,7 +6616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="26.25">
+    <row r="183" spans="1:11" ht="26.25" hidden="1">
       <c r="A183" s="13">
         <v>183</v>
       </c>
@@ -6649,7 +6643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="26.25">
+    <row r="184" spans="1:11" ht="26.25" hidden="1">
       <c r="A184" s="13">
         <v>184</v>
       </c>
@@ -6676,7 +6670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="39">
+    <row r="185" spans="1:11" ht="39" hidden="1">
       <c r="A185" s="13">
         <v>185</v>
       </c>
@@ -6703,7 +6697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="26.25">
+    <row r="186" spans="1:11" ht="26.25" hidden="1">
       <c r="A186" s="13">
         <v>186</v>
       </c>
@@ -6730,7 +6724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187" s="13">
         <v>187</v>
       </c>
@@ -6757,7 +6751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188" s="13">
         <v>188</v>
       </c>
@@ -6765,13 +6759,13 @@
         <v>11</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F188" s="11"/>
       <c r="G188" s="5">
@@ -6784,7 +6778,7 @@
       <c r="J188" s="8"/>
       <c r="K188" s="5"/>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189" s="13">
         <v>189</v>
       </c>
@@ -6792,13 +6786,13 @@
         <v>11</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F189" s="8"/>
       <c r="G189" s="5">
@@ -6813,7 +6807,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190" s="13">
         <v>190</v>
       </c>
@@ -6821,13 +6815,13 @@
         <v>11</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="5">
@@ -6842,7 +6836,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191" s="13">
         <v>191</v>
       </c>
@@ -6850,13 +6844,13 @@
         <v>11</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F191" s="8"/>
       <c r="G191" s="5">
@@ -6871,7 +6865,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" hidden="1">
       <c r="A192" s="13">
         <v>192</v>
       </c>
@@ -6879,13 +6873,13 @@
         <v>11</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="5">
@@ -6900,7 +6894,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" hidden="1">
       <c r="A193" s="13">
         <v>193</v>
       </c>
@@ -6908,13 +6902,13 @@
         <v>11</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F193" s="8"/>
       <c r="G193" s="5">
@@ -6929,7 +6923,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" hidden="1">
       <c r="A194" s="13">
         <v>194</v>
       </c>
@@ -6937,13 +6931,13 @@
         <v>11</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="5">
@@ -6958,7 +6952,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" hidden="1">
       <c r="A195" s="13">
         <v>195</v>
       </c>
@@ -6966,13 +6960,13 @@
         <v>11</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F195" s="8"/>
       <c r="G195" s="5">
@@ -6987,7 +6981,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" hidden="1">
       <c r="A196" s="13">
         <v>196</v>
       </c>
@@ -6995,13 +6989,13 @@
         <v>11</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="5">
@@ -7016,7 +7010,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" hidden="1">
       <c r="A197" s="13">
         <v>197</v>
       </c>
@@ -7024,13 +7018,13 @@
         <v>11</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F197" s="8"/>
       <c r="G197" s="5">
@@ -7045,7 +7039,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" hidden="1">
       <c r="A198" s="13">
         <v>199</v>
       </c>
@@ -7053,13 +7047,13 @@
         <v>11</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="5">
@@ -7074,7 +7068,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" hidden="1">
       <c r="A199" s="13">
         <v>200</v>
       </c>
@@ -7082,13 +7076,13 @@
         <v>11</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F199" s="8"/>
       <c r="G199" s="5">
@@ -7103,7 +7097,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" hidden="1">
       <c r="A200" s="13">
         <v>201</v>
       </c>
@@ -7111,13 +7105,13 @@
         <v>11</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="5">
@@ -7132,7 +7126,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" hidden="1">
       <c r="A201" s="13">
         <v>202</v>
       </c>
@@ -7140,13 +7134,13 @@
         <v>11</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F201" s="8"/>
       <c r="G201" s="5">
@@ -7161,7 +7155,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" hidden="1">
       <c r="A202" s="13">
         <v>203</v>
       </c>
@@ -7169,13 +7163,13 @@
         <v>11</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F202" s="8"/>
       <c r="G202" s="5">
@@ -7190,7 +7184,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" hidden="1">
       <c r="A203" s="13">
         <v>204</v>
       </c>
@@ -7198,13 +7192,13 @@
         <v>11</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F203" s="8"/>
       <c r="G203" s="5">
@@ -7219,7 +7213,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" hidden="1">
       <c r="A204" s="13">
         <v>205</v>
       </c>
@@ -7227,13 +7221,13 @@
         <v>11</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F204" s="8"/>
       <c r="G204" s="5">
@@ -7248,7 +7242,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" hidden="1">
       <c r="A205" s="13">
         <v>206</v>
       </c>
@@ -7256,13 +7250,13 @@
         <v>11</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F205" s="8"/>
       <c r="G205" s="5">
@@ -7277,7 +7271,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" hidden="1">
       <c r="A206" s="13">
         <v>207</v>
       </c>
@@ -7285,13 +7279,13 @@
         <v>11</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F206" s="8"/>
       <c r="G206" s="5">
@@ -7306,7 +7300,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" hidden="1">
       <c r="A207" s="13">
         <v>208</v>
       </c>
@@ -7314,13 +7308,13 @@
         <v>11</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D207" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F207" s="8"/>
       <c r="G207" s="5">
@@ -13544,11 +13538,17 @@
       <c r="J983" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K207" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K207" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Учет Pi 1 с.ш. ГРЩ1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1 G1:I8 K1:K2 K4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1 G9:I9 K1:K2 G1:I7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13571,30 +13571,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>290</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E2" s="4">
         <v>0.5</v>
@@ -13602,16 +13602,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E3" s="4">
         <v>0.3</v>
@@ -13637,104 +13637,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -13756,104 +13756,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
